--- a/human_validation/judge/kor/judge_D018_S001_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D018_S001_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,397 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 저를 찾아오시게 된 이유가 무엇인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 이 생각을 머릿속에서 떨쳐낼 수가 없어서 왔어요... 그 오랜 세월 전기 기술자로 일했는데도, 결국 제 동생 하나 안전하게 지키지 못했다는 생각이요. 그게 사실이라면, 저랑 같이 일하는 사람이든, 심지어 제 집에 사는 사람이든 저는 위험한 존재일지도 모른다는 생각이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 이 생각을 없애려고 뭔가를 반복해서 해야 한다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 그걸 멈추려고 정확히 반복하는 행동이 있는 것 같지는 않아요. 그 생각이 그냥 다시 돌아오고, 저는 거기에 갇혀요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 이 생각 때문에 특정한 것들이나 상황을 피해야 한다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 지금은 많은 걸 피해요. 정말 어쩔 수 없을 때가 아니면 제 차고에는 안 들어가요. 예전에 하던 교회 전기 작업도 그만뒀고요. 사람들이 자동차 프로젝트나 화재 얘기를 꺼내면 바로 대화를 끊어버려요. 그냥 감당이 안 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 동생과 관련된 이 생각 때문에 나쁜 일이 일어나는 걸 막으려고 뭔가를 하고 계시다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 모르겠어요. 그러니까, 말씀드렸듯이 뭔가를 피하긴 하는데, 나쁜 일이 일어나는 걸 막으려고 특정한 뭔가를 하고 있다고 생각하지는 않아요. 그보다는 특정 상황에서 제 자신을 못 믿어서 그냥 거리를 두는 거예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 생각을 없애려고 특정한 생각을 하거나 스스로에게 특정한 말을 해야 한다고 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 아니요, 그런 것 같지 않아요. 그걸 없애려고 반복하는 특정한 말이나 문구는 없어요. 그보다는 그 생각이 떠오르면 밀어내려고 하거나 그 원인이 된 것에서 벗어나려고 하는 거지, 스스로에게 특별한 말을 하는 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 생각이 떠오를 때, 기분이 나아지거나 불안을 덜기 위해 특정한 걸 생각하거나 해야 한다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 그렇지는 않아요. 그러니까, 거기서 벗어나거나 주의를 돌리려고 하긴 하는데, 진정하기 위해 꼭 해야 하거나 생각해야 하는 특정한 게 있는 건 아니에요. 그냥... 지나가길 기다리는 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 생각이 원치 않는데도 마음속에 들어오는 것처럼 느껴지시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네. 원하지 않을 때 들어와요. 전기 패널 배선 작업을 하면서 집중하고 있다가, 갑자기 다시 그 순간으로 돌아가요 — 연기 냄새가 나고, 동생이 보여요. 아니면 조카가 차고 문 닫는 소리를 들으면 그냥 확 덮쳐와요. 순간적으로 주변의 모든 게 사라지는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 생각에 대응해서, 덜 괴롭게 만들거나 나쁜 일이 일어나는 걸 막기 위해 뭔가를 해야 한다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 그렇지는 않은 것 같아요. 나쁜 일이 일어나는 걸 막으려고 해야 하는 어떤 행동이 있는 건 아니에요. 그게 떠오르면 그냥 속상해지고 그걸 버텨내거나 주의를 돌리려고 하는데, 그게 규칙이나 꼭 따라야 하는 의식 같은 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 생각이 들 때 특정한 행동을 해야 한다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 아니요, 특별히 해야 하는 행동은 없는 것 같아요. 하던 걸 멈추거나 주의를 돌리려고 할 수는 있지만, 매번 꼭 해야 하는 어떤 정해진 행동이 있는 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 생각이 들 때 꼭 해야만 하는 뭔가가 있다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 아니요... 꼭 해야 하는 게 있는 것 같지는 않아요. 그보다는 그 생각에 부딪히면 스스로를 다잡으려고 하는 건데, 꼭 해야 한다고 느끼는 특정한 게 있는 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 생각이 마음속에 떠오를 때 속상하거나 괴로움을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네. 세게 와닿아요. 가슴이 무거워지는 죄책감이랑 분노가 밀려오는데, 그게 하루 대부분 그 자리에 있어요. 조카를 보면서 이런 생각이 들 때 더 심해져요... 아버지를 잃었는데, 이제는 저랑 같이 살아야 하는구나 하는 생각이요. 그 생각이 저를 정말 힘들게 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 동생의 사고가 났던 순간이 마치 다시 일어나는 것처럼 다시 겪는 느낌이 든 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네. 아무 때나 갑자기 그럴 수 있어요. 전기 패널 배선 작업을 하고 있거나, 조카가 차고 문 닫는 소리를 들으면, 갑자기 다시 그때로 돌아간 것 같아요 — 연기 냄새가 나고, 동생이 보여요. 순간적으로 작업 현장이 발밑에서 꺼지는 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 동생의 사고가 났던 순간을 마치 다시 그 자리에 있는 것처럼 다시 겪게 되는 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 네... 말씀드렸듯이 그런 일이 있어요. 전기 패널 배선 작업 같은 평범한 걸 하고 있거나 조카가 차고 문 닫는 소리를 들으면, 갑자기 그때로 돌아가요. 연기 냄새를 맡고, 동생을 보고, 순간적으로 주변의 모든 게 사라지는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 동생이나 사고에 대해 다른 사람들과 얘기하는 걸 피하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 네. 가능하면 동생이나 사고에 대해 얘기하지 않으려고 해요. 사람들이 화재나 자동차 프로젝트 얘기를 꺼내면 바로 끊어버려요. 정말 어쩔 수 없을 때가 아니면 제 차고에는 안 들어가고, 교회 전기 작업도 그만뒀어요, 너무 많은 걸 다시 떠올리게 해서요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 동생의 사고에 대한 악몽을 꾸시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 네. 거의 매일 밤 이미 긴장한 채로 누워서 뭔가 갈라지는 소리나 밖의 차 문 소리 같은 걸 신경 써서 듣고 있어요. 그리고 잠이 들면, 차고에 대한 꿈을 꿔요... 그러고는 식은땀에 흠뻑 젖어서 깜짝 깨요. 그 후엔 보통 출근 전까지 다시 잠들지 못해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 이런 생각과 감정을 얼마나 오랫동안 겪고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 이제 4개월쯤 됐어요. 차고 화재 이후에 시작됐어요... 그리고 조카가 저희 집에 살러 온 후에요. 그 이후로 동생을 안전하게 지키지 못했다는 그 생각들이 계속 거기 있었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 차고에 들어가거나 동생과 사고에 대해 얘기하는 걸 피하신 지는 얼마나 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 한 4개월쯤 됐어요. 차고 화재가 일어나고 조카가 저희 집에 살러 온 후부터, 그 모든 걸 피해왔어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 동생의 사고에 대한 악몽을 꾸신 지는 얼마나 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 한 4개월쯤 됐어요. 차고 화재 이후에 시작돼서, 조카가 저희 집에 살러 온 무렵부터, 그 이후로 계속 그래요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>진단명: 외상후 스트레스장애 (D018)
 인구통계: 성별 남성 / 나이 42 / 직업상태 electrician / 최종학력 대학 재학
@@ -575,464 +957,45 @@
 증상 지속 기간: 4 months
 추가 요건: 
 주호소 증상 코드: S072
-배경 서술: 헨리는 동생이 관련된 치명적인 차고 화재 현장에 처음 도착한 후 십대 조카를 데려와 함께 살게 되었고, 그로 인해 새로운 가족 구성원의 등장이 외상적인 상실과 화재의 광경, 소리와 떼려야 뗄 수 없게 되었다. 그 후 4개월 동안, 평소의 말 많고 자신감 있던 모습이 무너지면서 수면 장애, 침투적인 기억, 자신의 차고와 교회 전기 작업, 자동차 복원 작업 공간에 대한 회피, 자신의 기술로는 누구도 안전하게 지킬 수 없다는 경직된 믿음, 지속적인 죄책감과 분노, 점점 심해지는 언어적 폭발, 운전과 살아있는 전기 작업 관련한 무모한 행동으로 이어졌다. 견습생들이 그와 짝이 되기를 거부하고 한 도급업체가 위험한 대립 이후 그를 태양광 설치 현장에서 제외시키면서 일자리를 잃기 시작하자 이 상태는 임상적으로 유의미해졌다. 그는 현장 안전 자격과 연계된 산업보건 의뢰를 통해 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 저를 찾아오시게 된 이유가 무엇인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 이 생각을 머릿속에서 떨쳐낼 수가 없어서 왔어요... 그 오랜 세월 전기 기술자로 일했는데도, 결국 제 동생 하나 안전하게 지키지 못했다는 생각이요. 그게 사실이라면, 저랑 같이 일하는 사람이든, 심지어 제 집에 사는 사람이든 저는 위험한 존재일지도 모른다는 생각이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 이 생각을 없애려고 뭔가를 반복해서 해야 한다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 그걸 멈추려고 정확히 반복하는 행동이 있는 것 같지는 않아요. 그 생각이 그냥 다시 돌아오고, 저는 거기에 갇혀요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 이 생각 때문에 특정한 것들이나 상황을 피해야 한다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 지금은 많은 걸 피해요. 정말 어쩔 수 없을 때가 아니면 제 차고에는 안 들어가요. 예전에 하던 교회 전기 작업도 그만뒀고요. 사람들이 자동차 프로젝트나 화재 얘기를 꺼내면 바로 대화를 끊어버려요. 그냥 감당이 안 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 동생과 관련된 이 생각 때문에 나쁜 일이 일어나는 걸 막으려고 뭔가를 하고 계시다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 모르겠어요. 그러니까, 말씀드렸듯이 뭔가를 피하긴 하는데, 나쁜 일이 일어나는 걸 막으려고 특정한 뭔가를 하고 있다고 생각하지는 않아요. 그보다는 특정 상황에서 제 자신을 못 믿어서 그냥 거리를 두는 거예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 생각을 없애려고 특정한 생각을 하거나 스스로에게 특정한 말을 해야 한다고 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 아니요, 그런 것 같지 않아요. 그걸 없애려고 반복하는 특정한 말이나 문구는 없어요. 그보다는 그 생각이 떠오르면 밀어내려고 하거나 그 원인이 된 것에서 벗어나려고 하는 거지, 스스로에게 특별한 말을 하는 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 생각이 떠오를 때, 기분이 나아지거나 불안을 덜기 위해 특정한 걸 생각하거나 해야 한다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 그렇지는 않아요. 그러니까, 거기서 벗어나거나 주의를 돌리려고 하긴 하는데, 진정하기 위해 꼭 해야 하거나 생각해야 하는 특정한 게 있는 건 아니에요. 그냥... 지나가길 기다리는 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 생각이 원치 않는데도 마음속에 들어오는 것처럼 느껴지시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네. 원하지 않을 때 들어와요. 전기 패널 배선 작업을 하면서 집중하고 있다가, 갑자기 다시 그 순간으로 돌아가요 — 연기 냄새가 나고, 동생이 보여요. 아니면 조카가 차고 문 닫는 소리를 들으면 그냥 확 덮쳐와요. 순간적으로 주변의 모든 게 사라지는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 생각에 대응해서, 덜 괴롭게 만들거나 나쁜 일이 일어나는 걸 막기 위해 뭔가를 해야 한다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 그렇지는 않은 것 같아요. 나쁜 일이 일어나는 걸 막으려고 해야 하는 어떤 행동이 있는 건 아니에요. 그게 떠오르면 그냥 속상해지고 그걸 버텨내거나 주의를 돌리려고 하는데, 그게 규칙이나 꼭 따라야 하는 의식 같은 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 생각이 들 때 특정한 행동을 해야 한다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 아니요, 특별히 해야 하는 행동은 없는 것 같아요. 하던 걸 멈추거나 주의를 돌리려고 할 수는 있지만, 매번 꼭 해야 하는 어떤 정해진 행동이 있는 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 생각이 들 때 꼭 해야만 하는 뭔가가 있다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 아니요... 꼭 해야 하는 게 있는 것 같지는 않아요. 그보다는 그 생각에 부딪히면 스스로를 다잡으려고 하는 건데, 꼭 해야 한다고 느끼는 특정한 게 있는 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 생각이 마음속에 떠오를 때 속상하거나 괴로움을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네. 세게 와닿아요. 가슴이 무거워지는 죄책감이랑 분노가 밀려오는데, 그게 하루 대부분 그 자리에 있어요. 조카를 보면서 이런 생각이 들 때 더 심해져요... 아버지를 잃었는데, 이제는 저랑 같이 살아야 하는구나 하는 생각이요. 그 생각이 저를 정말 힘들게 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 동생의 사고가 났던 순간이 마치 다시 일어나는 것처럼 다시 겪는 느낌이 든 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네. 아무 때나 갑자기 그럴 수 있어요. 전기 패널 배선 작업을 하고 있거나, 조카가 차고 문 닫는 소리를 들으면, 갑자기 다시 그때로 돌아간 것 같아요 — 연기 냄새가 나고, 동생이 보여요. 순간적으로 작업 현장이 발밑에서 꺼지는 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 동생의 사고가 났던 순간을 마치 다시 그 자리에 있는 것처럼 다시 겪게 되는 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 네... 말씀드렸듯이 그런 일이 있어요. 전기 패널 배선 작업 같은 평범한 걸 하고 있거나 조카가 차고 문 닫는 소리를 들으면, 갑자기 그때로 돌아가요. 연기 냄새를 맡고, 동생을 보고, 순간적으로 주변의 모든 게 사라지는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 동생이나 사고에 대해 다른 사람들과 얘기하는 걸 피하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 네. 가능하면 동생이나 사고에 대해 얘기하지 않으려고 해요. 사람들이 화재나 자동차 프로젝트 얘기를 꺼내면 바로 끊어버려요. 정말 어쩔 수 없을 때가 아니면 제 차고에는 안 들어가고, 교회 전기 작업도 그만뒀어요, 너무 많은 걸 다시 떠올리게 해서요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 동생의 사고에 대한 악몽을 꾸시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 네. 거의 매일 밤 이미 긴장한 채로 누워서 뭔가 갈라지는 소리나 밖의 차 문 소리 같은 걸 신경 써서 듣고 있어요. 그리고 잠이 들면, 차고에 대한 꿈을 꿔요... 그러고는 식은땀에 흠뻑 젖어서 깜짝 깨요. 그 후엔 보통 출근 전까지 다시 잠들지 못해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 외상후 스트레스장애 (D018) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 동생을 안전하게 지키지 못했다는 이런 생각과 감정을 얼마나 오랫동안 겪고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 이제 4개월쯤 됐어요. 차고 화재 이후에 시작됐어요... 그리고 조카가 저희 집에 살러 온 후에요. 그 이후로 동생을 안전하게 지키지 못했다는 그 생각들이 계속 거기 있었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 외상후 스트레스장애 (D018) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 차고에 들어가거나 동생과 사고에 대해 얘기하는 걸 피하신 지는 얼마나 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 한 4개월쯤 됐어요. 차고 화재가 일어나고 조카가 저희 집에 살러 온 후부터, 그 모든 걸 피해왔어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 외상후 스트레스장애 (D018) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 동생의 사고에 대한 악몽을 꾸신 지는 얼마나 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 한 4개월쯤 됐어요. 차고 화재 이후에 시작돼서, 조카가 저희 집에 살러 온 무렵부터, 그 이후로 계속 그래요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
+배경 서술: 헨리는 동생이 관련된 치명적인 차고 화재 현장에 처음 도착한 후 십대 조카를 데려와 함께 살게 되었고, 그로 인해 새로운 가족 구성원의 등장이 외상적인 상실과 화재의 광경, 소리와 떼려야 뗄 수 없게 되었다. 그 후 4개월 동안, 평소의 말 많고 자신감 있던 모습이 무너지면서 수면 장애, 침투적인 기억, 자신의 차고와 교회 전기 작업, 자동차 복원 작업 공간에 대한 회피, 자신의 기술로는 누구도 안전하게 지킬 수 없다는 경직된 믿음, 지속적인 죄책감과 분노, 점점 심해지는 언어적 폭발, 운전과 살아있는 전기 작업 관련한 무모한 행동으로 이어졌다. 견습생들이 그와 짝이 되기를 거부하고 한 도급업체가 위험한 대립 이후 그를 태양광 설치 현장에서 제외시키면서 일자리를 잃기 시작하자 이 상태는 임상적으로 유의미해졌다. 그는 현장 안전 자격과 연계된 산업보건 의뢰를 통해 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S069 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.
+  - S070 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.
+  - S072 부정적 신념: 자신, 타인, 세상에 대한 지속적이고 과장된 부정적 믿음이나 기대.
+  - S074 지속적인 부정적 정서 상태: 지속적인 부정적 정서 상태(예: 두려움, 공포, 분노, 죄책감, 수치심).
+  - S077 과민성/공격성: 사소하거나 별다른 도발 없이도 언어적·신체적 공격성으로 나타나는 과민한 행동과 분노 폭발.
+  - S078 무모/자기파괴적 행동: 자신의 안전이나 건강을 위태롭게 하는 무모하거나 자기파괴적인 행동 양상.</t>
+        </is>
+      </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 외상후 스트레스장애 (D018) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 외상후 스트레스장애 (D018, ICD: F43.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: trauma_related_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.; 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.
-  누락: (없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: trauma_related_alterations (관계=must_include, 요구개수=2, 충족개수=3, 커버리지=1.0)
-  확인된 근거: 부정적 신념: 자신, 타인, 세상에 대한 지속적이고 과장된 부정적 믿음이나 기대.; 왜곡된 인지와 비난: 외상 사건의 원인이나 결과에 대해 지속적이고 왜곡된 인지를 가지고 있어 자신이나 타인을 비난하게 됨.; 지속적인 부정적 정서 상태: 지속적인 부정적 정서 상태(예: 두려움, 공포, 분노, 죄책감, 수치심).
-  누락: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 외상 관련 기억상실: 외상 사건의 중요한 부분을 기억하지 못함(통상 해리성 기억상실에 의한 것으로, 두부 손상이나 알코올 등 다른 요인에 의한 것이 아님).; 사회적 유리감: 타인으로부터 동떨어지거나 소외된 느낌.; 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: arousal_and_reactivity (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 과각성: 주변 환경에 대해 지속적으로 경계하고 긴장하는 상태.
-  누락: 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 과민성/공격성: 사소하거나 별다른 도발 없이도 언어적·신체적 공격성으로 나타나는 과민한 행동과 분노 폭발.; 무모/자기파괴적 행동: 자신의 안전이나 건강을 위태롭게 하는 무모하거나 자기파괴적인 행동 양상.; 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.</t>
+          <t>의사의 최종 진단: 외상후 스트레스장애 (D018, ICD: F43.1)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: trauma_related_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.
+  - 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.
+체크리스트 그룹: trauma_related_alterations (관계=must_include, 요구개수=2, 충족개수=3, 커버리지=1.0)
+확인된 근거:
+  - 부정적 신념: 자신, 타인, 세상에 대한 지속적이고 과장된 부정적 믿음이나 기대.
+  - 왜곡된 인지와 비난: 외상 사건의 원인이나 결과에 대해 지속적이고 왜곡된 인지를 가지고 있어 자신이나 타인을 비난하게 됨.
+  - 지속적인 부정적 정서 상태: 지속적인 부정적 정서 상태(예: 두려움, 공포, 분노, 죄책감, 수치심).
+체크리스트 그룹: arousal_and_reactivity (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - 과각성: 주변 환경에 대해 지속적으로 경계하고 긴장하는 상태.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A70:B70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D018_S001_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D018_S001_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -943,6 +943,11 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -991,11 +996,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A70:B70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D018_S001_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D018_S001_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.2546</v>
+        <v>0.4583</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.3611</v>
+        <v>0.5648</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
